--- a/SSA/AWS/Summary_Filled.xlsx
+++ b/SSA/AWS/Summary_Filled.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeeshan.ali\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Syed Zeeshan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81B4DE4-E14E-470C-9829-615033954CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9600"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$33</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="897">
   <si>
     <t>S.No.</t>
   </si>
@@ -442,21 +449,6 @@
     <t>Amazon Route 53</t>
   </si>
   <si>
-    <t>Amazon Route 53 is a highly available and scalable Domain Name System (DNS) web service that routes users to applications and AWS resources.</t>
-  </si>
-  <si>
-    <t>To translate domain names into IP addresses, direct traffic to the correct resources, improve availability, and support disaster recovery.</t>
-  </si>
-  <si>
-    <t>Whenever you need domain registration, DNS management, traffic routing, health checks, or global application routing.</t>
-  </si>
-  <si>
-    <t>Unlike CloudFront (content delivery), Route 53 only resolves DNS. Unlike ELB (traffic distribution), Route 53 determines where traffic should go.</t>
-  </si>
-  <si>
-    <t>User → Route 53 DNS Query → Routing Policy → ALB/CloudFront/API Gateway/S3/EC2</t>
-  </si>
-  <si>
     <t>1. User opens website</t>
   </si>
   <si>
@@ -553,24 +545,6 @@
     <t xml:space="preserve">    KMS</t>
   </si>
   <si>
-    <t>Amazon EBS (Elastic Block Store)</t>
-  </si>
-  <si>
-    <t>Amazon EBS is a persistent block storage service designed for use with Amazon EC2 instances. It provides virtual hard disks that can be attached to EC2 servers.</t>
-  </si>
-  <si>
-    <t>To provide durable, high-performance storage for operating systems, applications, databases, and files that require persistent storage.</t>
-  </si>
-  <si>
-    <t>When EC2 instances need a boot volume, database storage, application storage, or low-latency block storage that persists after instance restarts.</t>
-  </si>
-  <si>
-    <t>Unlike S3 (object storage), EBS provides block storage. Unlike EFS (shared file storage), EBS is typically attached to a single EC2 instance. EBS is ideal for databases and operating systems, while S3 is ideal for files and backups.</t>
-  </si>
-  <si>
-    <t>EC2 Instance → EBS Volume → Snapshots (S3) → Backup/Recovery</t>
-  </si>
-  <si>
     <t>AWS Snowball Edge</t>
   </si>
   <si>
@@ -623,13 +597,2157 @@
   </si>
   <si>
     <t>Data in S3 → AWS Glue Data Catalog → Athena SQL Query → Results</t>
+  </si>
+  <si>
+    <t>AWS Organizations</t>
+  </si>
+  <si>
+    <t>AWS Organizations is an account management service that enables centralized governance, security, billing, and policy management across multiple AWS accounts.</t>
+  </si>
+  <si>
+    <t>To manage multiple AWS accounts from a single place, enforce security controls, apply governance policies, and consolidate billing.</t>
+  </si>
+  <si>
+    <t>When an organization has multiple AWS accounts for different teams, environments, business units, projects, or compliance requirements.</t>
+  </si>
+  <si>
+    <t>Unlike managing accounts individually, AWS Organizations provides centralized administration. It works with IAM, SCPs, Control Tower, and consolidated billing to enforce governance at scale.</t>
+  </si>
+  <si>
+    <t>AWS Organization → Organizational Units (OUs) → AWS Accounts → IAM/SCP Policies → AWS Resources</t>
+  </si>
+  <si>
+    <t>NFS (Network File System)</t>
+  </si>
+  <si>
+    <t>NFS is a file-sharing protocol that allows multiple servers to access the same files over a network as if they were stored locally.</t>
+  </si>
+  <si>
+    <t>To provide shared file storage across multiple servers simultaneously.</t>
+  </si>
+  <si>
+    <t>When multiple EC2 instances need access to the same files, application content, user uploads, shared configuration files, or home directories.</t>
+  </si>
+  <si>
+    <t>Unlike EBS (block storage), NFS supports concurrent access by multiple servers. Unlike S3 (object storage), NFS behaves like a traditional file system with folders and files. AWS EFS uses NFS.</t>
+  </si>
+  <si>
+    <t>Multiple EC2 Instances → NFS Mount → Shared File System (EFS)</t>
+  </si>
+  <si>
+    <t>Amazon EventBridge</t>
+  </si>
+  <si>
+    <t>Amazon EventBridge is a serverless event bus service that enables applications, AWS services, and SaaS applications to communicate through events and route them to targets using rules.</t>
+  </si>
+  <si>
+    <t>To build event-driven architectures, decouple applications, automate workflows, and route events between services without custom integration code.</t>
+  </si>
+  <si>
+    <t>When applications need to react to events, trigger workflows, integrate AWS services, connect SaaS applications, or coordinate microservices.</t>
+  </si>
+  <si>
+    <t>Unlike SNS, EventBridge supports content-based filtering and advanced routing rules. Unlike SQS, EventBridge is not a queue. Unlike Kinesis, it is not designed for high-throughput streaming analytics.</t>
+  </si>
+  <si>
+    <t>Event Source → EventBridge Event Bus → Rules → Targets (Lambda, SQS, SNS, Step Functions, ECS, etc.)</t>
+  </si>
+  <si>
+    <t>AWS CloudTrail is a governance, compliance, and auditing service that records AWS API calls, user activities, account actions, and resource changes across your AWS environment.</t>
+  </si>
+  <si>
+    <t>To track who did what, when they did it, from where they did it, and what resources were affected. It is essential for auditing, security investigations, compliance, and operational troubleshooting.</t>
+  </si>
+  <si>
+    <t>When you need audit logs, compliance reporting, security monitoring, forensic analysis, or activity tracking across AWS accounts.</t>
+  </si>
+  <si>
+    <t>Unlike CloudWatch, which monitors performance and metrics, CloudTrail records API activity. Unlike AWS Config, which tracks configuration changes, CloudTrail tracks who made those changes.</t>
+  </si>
+  <si>
+    <t>User/API Call → CloudTrail → S3 Bucket → CloudWatch Logs/SNS/SIEM → Monitoring &amp; Auditing</t>
+  </si>
+  <si>
+    <t>Amazon CloudWatch is a monitoring and observability service that collects metrics, logs, events, and traces from AWS resources and applications to monitor performance, detect issues, and automate responses.</t>
+  </si>
+  <si>
+    <t>To monitor infrastructure and applications, create alerts, visualize metrics, troubleshoot problems, and automate operational actions.</t>
+  </si>
+  <si>
+    <t>When monitoring EC2, RDS, Lambda, ECS, API Gateway, custom applications, or any AWS workload requiring visibility into performance and health.</t>
+  </si>
+  <si>
+    <t>Unlike CloudTrail, which tracks API activity, CloudWatch tracks performance and operational metrics. Unlike AWS Config, which tracks configuration changes, CloudWatch monitors resource health and behavior.</t>
+  </si>
+  <si>
+    <t>AWS Resources → CloudWatch Metrics/Logs → Alarms → SNS/Lambda/Auto Scaling → Notifications/Actions</t>
+  </si>
+  <si>
+    <t>Tier 1: Must Master (80% of Interview Questions)</t>
+  </si>
+  <si>
+    <t>These are the services I would expect a Solution Architect to know thoroughly.</t>
+  </si>
+  <si>
+    <t>Compute</t>
+  </si>
+  <si>
+    <t>AWS Fargate</t>
+  </si>
+  <si>
+    <t>Know:</t>
+  </si>
+  <si>
+    <t>When to use each</t>
+  </si>
+  <si>
+    <t>Scaling</t>
+  </si>
+  <si>
+    <t>Cost implications</t>
+  </si>
+  <si>
+    <t>High availability patterns</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Amazon S3</t>
+  </si>
+  <si>
+    <t>Amazon EBS</t>
+  </si>
+  <si>
+    <t>Amazon EFS</t>
+  </si>
+  <si>
+    <t>Use Case</t>
+  </si>
+  <si>
+    <t>Object storage</t>
+  </si>
+  <si>
+    <t>Single server disk</t>
+  </si>
+  <si>
+    <t>Shared file system</t>
+  </si>
+  <si>
+    <t>Databases</t>
+  </si>
+  <si>
+    <t>Amazon RDS</t>
+  </si>
+  <si>
+    <t>SQL vs NoSQL</t>
+  </si>
+  <si>
+    <t>Multi-AZ</t>
+  </si>
+  <si>
+    <t>Read replicas</t>
+  </si>
+  <si>
+    <t>Backup strategies</t>
+  </si>
+  <si>
+    <t>Networking (Most Important Area)</t>
+  </si>
+  <si>
+    <t>VPC</t>
+  </si>
+  <si>
+    <t>Subnets</t>
+  </si>
+  <si>
+    <t>Route Tables</t>
+  </si>
+  <si>
+    <t>Security Groups</t>
+  </si>
+  <si>
+    <t>NACLs</t>
+  </si>
+  <si>
+    <t>Internet Gateway</t>
+  </si>
+  <si>
+    <t>NAT Gateway</t>
+  </si>
+  <si>
+    <t>VPC Endpoints</t>
+  </si>
+  <si>
+    <t>Transit Gateway</t>
+  </si>
+  <si>
+    <t>Direct Connect</t>
+  </si>
+  <si>
+    <t>Know these extremely well.</t>
+  </si>
+  <si>
+    <t>Many architect interviews focus heavily on networking.</t>
+  </si>
+  <si>
+    <t>Load Balancers</t>
+  </si>
+  <si>
+    <t>Elastic Load Balancing</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>HTTP/HTTPS</t>
+  </si>
+  <si>
+    <t>NLB</t>
+  </si>
+  <si>
+    <t>TCP/UDP</t>
+  </si>
+  <si>
+    <t>GWLB</t>
+  </si>
+  <si>
+    <t>Firewalls</t>
+  </si>
+  <si>
+    <t>DNS</t>
+  </si>
+  <si>
+    <t>Hosted zones</t>
+  </si>
+  <si>
+    <t>Routing policies</t>
+  </si>
+  <si>
+    <t>Failover</t>
+  </si>
+  <si>
+    <t>Health checks</t>
+  </si>
+  <si>
+    <t>IAM &amp; Security</t>
+  </si>
+  <si>
+    <t>AWS Identity and Access Management</t>
+  </si>
+  <si>
+    <t>AWS IAM Identity Center</t>
+  </si>
+  <si>
+    <t>AWS Key Management Service</t>
+  </si>
+  <si>
+    <t>AWS Secrets Manager</t>
+  </si>
+  <si>
+    <t>You must know these very well.</t>
+  </si>
+  <si>
+    <t>Tier 2: Very Common in Real Projects</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Messaging</t>
+  </si>
+  <si>
+    <t>Amazon SQS</t>
+  </si>
+  <si>
+    <t>Amazon SNS</t>
+  </si>
+  <si>
+    <t>These appear frequently in modern architectures.</t>
+  </si>
+  <si>
+    <t>Caching</t>
+  </si>
+  <si>
+    <t>Redis basics</t>
+  </si>
+  <si>
+    <t>CDN</t>
+  </si>
+  <si>
+    <t>Very common in interviews.</t>
+  </si>
+  <si>
+    <t>Tier 3: Important for Senior Architect Roles</t>
+  </si>
+  <si>
+    <t>Containers</t>
+  </si>
+  <si>
+    <t>ECS</t>
+  </si>
+  <si>
+    <t>Fargate</t>
+  </si>
+  <si>
+    <t>Amazon EKS</t>
+  </si>
+  <si>
+    <t>Since you already have Kubernetes experience, this is valuable.</t>
+  </si>
+  <si>
+    <t>Hybrid &amp; Migration</t>
+  </si>
+  <si>
+    <t>AWS DataSync</t>
+  </si>
+  <si>
+    <t>AWS Storage Gateway</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>AWS Glue</t>
+  </si>
+  <si>
+    <t>Know what each does.</t>
+  </si>
+  <si>
+    <t>Tier 4: Know at a High Level</t>
+  </si>
+  <si>
+    <t>You don't need deep expertise but should know when to recommend them.</t>
+  </si>
+  <si>
+    <t>Amazon EMR</t>
+  </si>
+  <si>
+    <t>Amazon OpenSearch Service</t>
+  </si>
+  <si>
+    <t>Amazon FSx</t>
+  </si>
+  <si>
+    <t>AWS Control Tower</t>
+  </si>
+  <si>
+    <t>AWS Network Firewall</t>
+  </si>
+  <si>
+    <t>For Your Background</t>
+  </si>
+  <si>
+    <t>Since you are a Senior Full Stack Developer / Team Lead with .NET, Azure, Docker, Kubernetes, and are preparing for AWS architecture roles, I would focus on:</t>
+  </si>
+  <si>
+    <t>Top 20 Services to Master</t>
+  </si>
+  <si>
+    <t>1. EC2</t>
+  </si>
+  <si>
+    <t>2. S3</t>
+  </si>
+  <si>
+    <t>3. RDS</t>
+  </si>
+  <si>
+    <t>4. Aurora</t>
+  </si>
+  <si>
+    <t>5. DynamoDB</t>
+  </si>
+  <si>
+    <t>6. VPC</t>
+  </si>
+  <si>
+    <t>7. Route 53</t>
+  </si>
+  <si>
+    <t>8. IAM</t>
+  </si>
+  <si>
+    <t>9. KMS</t>
+  </si>
+  <si>
+    <t>10. Lambda</t>
+  </si>
+  <si>
+    <t>11. ECS</t>
+  </si>
+  <si>
+    <t>12. Fargate</t>
+  </si>
+  <si>
+    <t>13. ALB/NLB/GWLB</t>
+  </si>
+  <si>
+    <t>14. CloudFront</t>
+  </si>
+  <si>
+    <t>15. CloudWatch</t>
+  </si>
+  <si>
+    <t>16. CloudTrail</t>
+  </si>
+  <si>
+    <t>17. SQS</t>
+  </si>
+  <si>
+    <t>18. SNS</t>
+  </si>
+  <si>
+    <t>19. EventBridge</t>
+  </si>
+  <si>
+    <t>20. Organizations</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If you can confidently design architectures using those 20 services, you'll be well prepared for most Solution Architect interviews and a large portion of day-to-day AWS architecture work. Knowing every AWS service is unnecessary; knowing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>when and why to use the right service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is what interviewers and employers care about.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kinesis Data Streams</t>
+  </si>
+  <si>
+    <t>Real-time streaming service that captures, stores, and processes streaming data with custom consumers.</t>
+  </si>
+  <si>
+    <t>To build custom real-time processing applications.</t>
+  </si>
+  <si>
+    <t>When applications need low-latency processing and custom consumers.</t>
+  </si>
+  <si>
+    <t>More flexible but requires consumer management.</t>
+  </si>
+  <si>
+    <t>Producers → Kinesis Data Streams → Consumers (Lambda, EC2, ECS)</t>
+  </si>
+  <si>
+    <t>Kinesis Data Firehose</t>
+  </si>
+  <si>
+    <t>Fully managed data delivery service that automatically loads streaming data into destinations.</t>
+  </si>
+  <si>
+    <t>To move streaming data to S3, Redshift, OpenSearch, etc., with minimal management.</t>
+  </si>
+  <si>
+    <t>When you simply want to ingest and store/analyze streaming data.</t>
+  </si>
+  <si>
+    <t>Easier to manage but less flexible.</t>
+  </si>
+  <si>
+    <t>Producers → Firehose → S3/Redshift/OpenSearch</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>das Haus</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>das Zimmer</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t>die Küche</t>
+  </si>
+  <si>
+    <t>kitchen</t>
+  </si>
+  <si>
+    <t>das Badezimmer</t>
+  </si>
+  <si>
+    <t>bathroom</t>
+  </si>
+  <si>
+    <t>das Schlafzimmer</t>
+  </si>
+  <si>
+    <t>bedroom</t>
+  </si>
+  <si>
+    <t>das Fenster</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>die Tür</t>
+  </si>
+  <si>
+    <t>door</t>
+  </si>
+  <si>
+    <t>der Tisch</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>der Stuhl</t>
+  </si>
+  <si>
+    <t>chair</t>
+  </si>
+  <si>
+    <t>das Bett</t>
+  </si>
+  <si>
+    <t>bed</t>
+  </si>
+  <si>
+    <t>der Schrank</t>
+  </si>
+  <si>
+    <t>wardrobe</t>
+  </si>
+  <si>
+    <t>das Sofa</t>
+  </si>
+  <si>
+    <t>sofa</t>
+  </si>
+  <si>
+    <t>die Lampe</t>
+  </si>
+  <si>
+    <t>lamp</t>
+  </si>
+  <si>
+    <t>der Spiegel</t>
+  </si>
+  <si>
+    <t>mirror</t>
+  </si>
+  <si>
+    <t>der Teppich</t>
+  </si>
+  <si>
+    <t>carpet</t>
+  </si>
+  <si>
+    <t>die Wand</t>
+  </si>
+  <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>die Decke</t>
+  </si>
+  <si>
+    <t>ceiling/blanket</t>
+  </si>
+  <si>
+    <t>der Boden</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>die Treppe</t>
+  </si>
+  <si>
+    <t>stairs</t>
+  </si>
+  <si>
+    <t>die Familie</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>der Vater</t>
+  </si>
+  <si>
+    <t>father</t>
+  </si>
+  <si>
+    <t>die Mutter</t>
+  </si>
+  <si>
+    <t>mother</t>
+  </si>
+  <si>
+    <t>der Sohn</t>
+  </si>
+  <si>
+    <t>son</t>
+  </si>
+  <si>
+    <t>die Tochter</t>
+  </si>
+  <si>
+    <t>daughter</t>
+  </si>
+  <si>
+    <t>der Bruder</t>
+  </si>
+  <si>
+    <t>brother</t>
+  </si>
+  <si>
+    <t>die Schwester</t>
+  </si>
+  <si>
+    <t>sister</t>
+  </si>
+  <si>
+    <t>der Opa</t>
+  </si>
+  <si>
+    <t>grandfather</t>
+  </si>
+  <si>
+    <t>die Oma</t>
+  </si>
+  <si>
+    <t>grandmother</t>
+  </si>
+  <si>
+    <t>der Onkel</t>
+  </si>
+  <si>
+    <t>uncle</t>
+  </si>
+  <si>
+    <t>die Tante</t>
+  </si>
+  <si>
+    <t>aunt</t>
+  </si>
+  <si>
+    <t>der Cousin</t>
+  </si>
+  <si>
+    <t>cousin (male)</t>
+  </si>
+  <si>
+    <t>die Cousine</t>
+  </si>
+  <si>
+    <t>cousin (female)</t>
+  </si>
+  <si>
+    <t>der Mann</t>
+  </si>
+  <si>
+    <t>man/husband</t>
+  </si>
+  <si>
+    <t>die Frau</t>
+  </si>
+  <si>
+    <t>woman/wife</t>
+  </si>
+  <si>
+    <t>das Kind</t>
+  </si>
+  <si>
+    <t>child</t>
+  </si>
+  <si>
+    <t>die Eltern</t>
+  </si>
+  <si>
+    <t>parents</t>
+  </si>
+  <si>
+    <t>der Freund</t>
+  </si>
+  <si>
+    <t>male friend</t>
+  </si>
+  <si>
+    <t>die Freundin</t>
+  </si>
+  <si>
+    <t>female friend</t>
+  </si>
+  <si>
+    <t>der Nachbar</t>
+  </si>
+  <si>
+    <t>neighbor</t>
+  </si>
+  <si>
+    <t>die Nachbarin</t>
+  </si>
+  <si>
+    <t>female neighbor</t>
+  </si>
+  <si>
+    <t>das Baby</t>
+  </si>
+  <si>
+    <t>baby</t>
+  </si>
+  <si>
+    <t>die Hochzeit</t>
+  </si>
+  <si>
+    <t>wedding</t>
+  </si>
+  <si>
+    <t>die Ehe</t>
+  </si>
+  <si>
+    <t>marriage</t>
+  </si>
+  <si>
+    <t>der Name</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>das Alter</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>das Mädchen</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>der Junge</t>
+  </si>
+  <si>
+    <t>boy</t>
+  </si>
+  <si>
+    <t>die Person</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t>die Geburt</t>
+  </si>
+  <si>
+    <t>birth</t>
+  </si>
+  <si>
+    <t>das Essen</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>das Brot</t>
+  </si>
+  <si>
+    <t>bread</t>
+  </si>
+  <si>
+    <t>der Reis</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>die Kartoffel</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>die Tomate</t>
+  </si>
+  <si>
+    <t>tomato</t>
+  </si>
+  <si>
+    <t>die Gurke</t>
+  </si>
+  <si>
+    <t>cucumber</t>
+  </si>
+  <si>
+    <t>der Salat</t>
+  </si>
+  <si>
+    <t>salad</t>
+  </si>
+  <si>
+    <t>der Apfel</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>die Banane</t>
+  </si>
+  <si>
+    <t>banana</t>
+  </si>
+  <si>
+    <t>die Orange</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>die Traube</t>
+  </si>
+  <si>
+    <t>grape</t>
+  </si>
+  <si>
+    <t>die Erdbeere</t>
+  </si>
+  <si>
+    <t>strawberry</t>
+  </si>
+  <si>
+    <t>das Ei</t>
+  </si>
+  <si>
+    <t>egg</t>
+  </si>
+  <si>
+    <t>das Fleisch</t>
+  </si>
+  <si>
+    <t>meat</t>
+  </si>
+  <si>
+    <t>das Hähnchen</t>
+  </si>
+  <si>
+    <t>chicken</t>
+  </si>
+  <si>
+    <t>der Fisch</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>der Käse</t>
+  </si>
+  <si>
+    <t>cheese</t>
+  </si>
+  <si>
+    <t>die Butter</t>
+  </si>
+  <si>
+    <t>butter</t>
+  </si>
+  <si>
+    <t>die Milch</t>
+  </si>
+  <si>
+    <t>milk</t>
+  </si>
+  <si>
+    <t>das Wasser</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>der Kaffee</t>
+  </si>
+  <si>
+    <t>coffee</t>
+  </si>
+  <si>
+    <t>der Tee</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>der Saft</t>
+  </si>
+  <si>
+    <t>juice</t>
+  </si>
+  <si>
+    <t>der Zucker</t>
+  </si>
+  <si>
+    <t>sugar</t>
+  </si>
+  <si>
+    <t>das Salz</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>der Pfeffer</t>
+  </si>
+  <si>
+    <t>pepper</t>
+  </si>
+  <si>
+    <t>die Suppe</t>
+  </si>
+  <si>
+    <t>soup</t>
+  </si>
+  <si>
+    <t>der Kuchen</t>
+  </si>
+  <si>
+    <t>cake</t>
+  </si>
+  <si>
+    <t>das Frühstück</t>
+  </si>
+  <si>
+    <t>breakfast</t>
+  </si>
+  <si>
+    <t>das Abendessen</t>
+  </si>
+  <si>
+    <t>dinner</t>
+  </si>
+  <si>
+    <t>das Auto</t>
+  </si>
+  <si>
+    <t>car</t>
+  </si>
+  <si>
+    <t>der Bus</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t>der Zug</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>das Fahrrad</t>
+  </si>
+  <si>
+    <t>bicycle</t>
+  </si>
+  <si>
+    <t>das Taxi</t>
+  </si>
+  <si>
+    <t>taxi</t>
+  </si>
+  <si>
+    <t>das Flugzeug</t>
+  </si>
+  <si>
+    <t>airplane</t>
+  </si>
+  <si>
+    <t>das Schiff</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>die U-Bahn</t>
+  </si>
+  <si>
+    <t>subway</t>
+  </si>
+  <si>
+    <t>die S-Bahn</t>
+  </si>
+  <si>
+    <t>suburban train</t>
+  </si>
+  <si>
+    <t>die Straßenbahn</t>
+  </si>
+  <si>
+    <t>tram</t>
+  </si>
+  <si>
+    <t>die Haltestelle</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>der Bahnhof</t>
+  </si>
+  <si>
+    <t>train station</t>
+  </si>
+  <si>
+    <t>der Flughafen</t>
+  </si>
+  <si>
+    <t>airport</t>
+  </si>
+  <si>
+    <t>die Reise</t>
+  </si>
+  <si>
+    <t>trip</t>
+  </si>
+  <si>
+    <t>das Ticket</t>
+  </si>
+  <si>
+    <t>ticket</t>
+  </si>
+  <si>
+    <t>die Straße</t>
+  </si>
+  <si>
+    <t>street</t>
+  </si>
+  <si>
+    <t>der Weg</t>
+  </si>
+  <si>
+    <t>way/path</t>
+  </si>
+  <si>
+    <t>die Brücke</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>der Fahrer</t>
+  </si>
+  <si>
+    <t>driver</t>
+  </si>
+  <si>
+    <t>das Motorrad</t>
+  </si>
+  <si>
+    <t>motorcycle</t>
+  </si>
+  <si>
+    <t>der Helm</t>
+  </si>
+  <si>
+    <t>helmet</t>
+  </si>
+  <si>
+    <t>die Ampel</t>
+  </si>
+  <si>
+    <t>traffic light</t>
+  </si>
+  <si>
+    <t>die Kreuzung</t>
+  </si>
+  <si>
+    <t>intersection</t>
+  </si>
+  <si>
+    <t>der Parkplatz</t>
+  </si>
+  <si>
+    <t>parking lot</t>
+  </si>
+  <si>
+    <t>das Benzin</t>
+  </si>
+  <si>
+    <t>gasoline</t>
+  </si>
+  <si>
+    <t>das Rad</t>
+  </si>
+  <si>
+    <t>wheel</t>
+  </si>
+  <si>
+    <t>die Karte</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>der Koffer</t>
+  </si>
+  <si>
+    <t>suitcase</t>
+  </si>
+  <si>
+    <t>die Tasche</t>
+  </si>
+  <si>
+    <t>bag</t>
+  </si>
+  <si>
+    <t>der Verkehr</t>
+  </si>
+  <si>
+    <t>traffic</t>
+  </si>
+  <si>
+    <t>die Schule</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>der Lehrer</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>die Lehrerin</t>
+  </si>
+  <si>
+    <t>female teacher</t>
+  </si>
+  <si>
+    <t>der Schüler</t>
+  </si>
+  <si>
+    <t>student</t>
+  </si>
+  <si>
+    <t>die Schülerin</t>
+  </si>
+  <si>
+    <t>female student</t>
+  </si>
+  <si>
+    <t>das Buch</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>das Heft</t>
+  </si>
+  <si>
+    <t>notebook</t>
+  </si>
+  <si>
+    <t>der Stift</t>
+  </si>
+  <si>
+    <t>pen</t>
+  </si>
+  <si>
+    <t>der Bleistift</t>
+  </si>
+  <si>
+    <t>pencil</t>
+  </si>
+  <si>
+    <t>der Radiergummi</t>
+  </si>
+  <si>
+    <t>eraser</t>
+  </si>
+  <si>
+    <t>das Lineal</t>
+  </si>
+  <si>
+    <t>ruler</t>
+  </si>
+  <si>
+    <t>die Schere</t>
+  </si>
+  <si>
+    <t>scissors</t>
+  </si>
+  <si>
+    <t>die Klasse</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>das Klassenzimmer</t>
+  </si>
+  <si>
+    <t>classroom</t>
+  </si>
+  <si>
+    <t>der Test</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>die Prüfung</t>
+  </si>
+  <si>
+    <t>exam</t>
+  </si>
+  <si>
+    <t>die Hausaufgabe</t>
+  </si>
+  <si>
+    <t>homework</t>
+  </si>
+  <si>
+    <t>die Frage</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>die Antwort</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>das Wort</t>
+  </si>
+  <si>
+    <t>word</t>
+  </si>
+  <si>
+    <t>der Satz</t>
+  </si>
+  <si>
+    <t>sentence</t>
+  </si>
+  <si>
+    <t>der Computer</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>der Bildschirm</t>
+  </si>
+  <si>
+    <t>screen</t>
+  </si>
+  <si>
+    <t>die Tafel</t>
+  </si>
+  <si>
+    <t>board</t>
+  </si>
+  <si>
+    <t>der Rucksack</t>
+  </si>
+  <si>
+    <t>backpack</t>
+  </si>
+  <si>
+    <t>das Papier</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>der Ordner</t>
+  </si>
+  <si>
+    <t>folder</t>
+  </si>
+  <si>
+    <t>die Pause</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>das Alphabet</t>
+  </si>
+  <si>
+    <t>alphabet</t>
+  </si>
+  <si>
+    <t>die Sprache</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>die Arbeit</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>der Beruf</t>
+  </si>
+  <si>
+    <t>profession</t>
+  </si>
+  <si>
+    <t>der Chef</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>die Chefin</t>
+  </si>
+  <si>
+    <t>female boss</t>
+  </si>
+  <si>
+    <t>der Kollege</t>
+  </si>
+  <si>
+    <t>colleague</t>
+  </si>
+  <si>
+    <t>die Kollegin</t>
+  </si>
+  <si>
+    <t>female colleague</t>
+  </si>
+  <si>
+    <t>das Büro</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>der Drucker</t>
+  </si>
+  <si>
+    <t>printer</t>
+  </si>
+  <si>
+    <t>die Firma</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>das Meeting</t>
+  </si>
+  <si>
+    <t>meeting</t>
+  </si>
+  <si>
+    <t>die E-Mail</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>der Kunde</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>die Kundin</t>
+  </si>
+  <si>
+    <t>female customer</t>
+  </si>
+  <si>
+    <t>das Projekt</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>die Aufgabe</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>der Termin</t>
+  </si>
+  <si>
+    <t>appointment</t>
+  </si>
+  <si>
+    <t>das Telefon</t>
+  </si>
+  <si>
+    <t>telephone</t>
+  </si>
+  <si>
+    <t>das Handy</t>
+  </si>
+  <si>
+    <t>mobile phone</t>
+  </si>
+  <si>
+    <t>der Mitarbeiter</t>
+  </si>
+  <si>
+    <t>employee</t>
+  </si>
+  <si>
+    <t>das Geld</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>das Gehalt</t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>die Bewerbung</t>
+  </si>
+  <si>
+    <t>application</t>
+  </si>
+  <si>
+    <t>der Lebenslauf</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>die Erfahrung</t>
+  </si>
+  <si>
+    <t>experience</t>
+  </si>
+  <si>
+    <t>der Vertrag</t>
+  </si>
+  <si>
+    <t>contract</t>
+  </si>
+  <si>
+    <t>die Rechnung</t>
+  </si>
+  <si>
+    <t>invoice</t>
+  </si>
+  <si>
+    <t>der Urlaub</t>
+  </si>
+  <si>
+    <t>vacation</t>
+  </si>
+  <si>
+    <t>die Karriere</t>
+  </si>
+  <si>
+    <t>career</t>
+  </si>
+  <si>
+    <t>das Wetter</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>die Sonne</t>
+  </si>
+  <si>
+    <t>sun</t>
+  </si>
+  <si>
+    <t>der Mond</t>
+  </si>
+  <si>
+    <t>moon</t>
+  </si>
+  <si>
+    <t>der Himmel</t>
+  </si>
+  <si>
+    <t>sky</t>
+  </si>
+  <si>
+    <t>die Wolke</t>
+  </si>
+  <si>
+    <t>cloud</t>
+  </si>
+  <si>
+    <t>der Regen</t>
+  </si>
+  <si>
+    <t>rain</t>
+  </si>
+  <si>
+    <t>der Schnee</t>
+  </si>
+  <si>
+    <t>snow</t>
+  </si>
+  <si>
+    <t>der Wind</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>der Sturm</t>
+  </si>
+  <si>
+    <t>storm</t>
+  </si>
+  <si>
+    <t>das Eis</t>
+  </si>
+  <si>
+    <t>ice</t>
+  </si>
+  <si>
+    <t>der Nebel</t>
+  </si>
+  <si>
+    <t>fog</t>
+  </si>
+  <si>
+    <t>die Hitze</t>
+  </si>
+  <si>
+    <t>heat</t>
+  </si>
+  <si>
+    <t>die Kälte</t>
+  </si>
+  <si>
+    <t>cold</t>
+  </si>
+  <si>
+    <t>die Temperatur</t>
+  </si>
+  <si>
+    <t>temperature</t>
+  </si>
+  <si>
+    <t>der Sommer</t>
+  </si>
+  <si>
+    <t>summer</t>
+  </si>
+  <si>
+    <t>der Winter</t>
+  </si>
+  <si>
+    <t>winter</t>
+  </si>
+  <si>
+    <t>der Frühling</t>
+  </si>
+  <si>
+    <t>spring</t>
+  </si>
+  <si>
+    <t>der Herbst</t>
+  </si>
+  <si>
+    <t>autumn</t>
+  </si>
+  <si>
+    <t>der Tag</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>die Nacht</t>
+  </si>
+  <si>
+    <t>night</t>
+  </si>
+  <si>
+    <t>der Morgen</t>
+  </si>
+  <si>
+    <t>morning</t>
+  </si>
+  <si>
+    <t>der Abend</t>
+  </si>
+  <si>
+    <t>evening</t>
+  </si>
+  <si>
+    <t>die Woche</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>der Monat</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>das Jahr</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>das Klima</t>
+  </si>
+  <si>
+    <t>climate</t>
+  </si>
+  <si>
+    <t>der Schirm</t>
+  </si>
+  <si>
+    <t>umbrella</t>
+  </si>
+  <si>
+    <t>die Jacke</t>
+  </si>
+  <si>
+    <t>jacket</t>
+  </si>
+  <si>
+    <t>die Jahreszeit</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>das Meer</t>
+  </si>
+  <si>
+    <t>sea</t>
+  </si>
+  <si>
+    <t>die Kleidung</t>
+  </si>
+  <si>
+    <t>clothing</t>
+  </si>
+  <si>
+    <t>das Hemd</t>
+  </si>
+  <si>
+    <t>shirt</t>
+  </si>
+  <si>
+    <t>das T-Shirt</t>
+  </si>
+  <si>
+    <t>T-shirt</t>
+  </si>
+  <si>
+    <t>die Hose</t>
+  </si>
+  <si>
+    <t>trousers</t>
+  </si>
+  <si>
+    <t>der Rock</t>
+  </si>
+  <si>
+    <t>skirt</t>
+  </si>
+  <si>
+    <t>das Kleid</t>
+  </si>
+  <si>
+    <t>dress</t>
+  </si>
+  <si>
+    <t>der Mantel</t>
+  </si>
+  <si>
+    <t>coat</t>
+  </si>
+  <si>
+    <t>der Pullover</t>
+  </si>
+  <si>
+    <t>sweater</t>
+  </si>
+  <si>
+    <t>die Socke</t>
+  </si>
+  <si>
+    <t>sock</t>
+  </si>
+  <si>
+    <t>der Schuh</t>
+  </si>
+  <si>
+    <t>shoe</t>
+  </si>
+  <si>
+    <t>der Hut</t>
+  </si>
+  <si>
+    <t>hat</t>
+  </si>
+  <si>
+    <t>die Mütze</t>
+  </si>
+  <si>
+    <t>cap</t>
+  </si>
+  <si>
+    <t>der Gürtel</t>
+  </si>
+  <si>
+    <t>belt</t>
+  </si>
+  <si>
+    <t>die Brille</t>
+  </si>
+  <si>
+    <t>glasses</t>
+  </si>
+  <si>
+    <t>die Uhr</t>
+  </si>
+  <si>
+    <t>watch</t>
+  </si>
+  <si>
+    <t>der Ring</t>
+  </si>
+  <si>
+    <t>ring</t>
+  </si>
+  <si>
+    <t>die Kette</t>
+  </si>
+  <si>
+    <t>necklace</t>
+  </si>
+  <si>
+    <t>das Armband</t>
+  </si>
+  <si>
+    <t>bracelet</t>
+  </si>
+  <si>
+    <t>der Handschuh</t>
+  </si>
+  <si>
+    <t>glove</t>
+  </si>
+  <si>
+    <t>der Schal</t>
+  </si>
+  <si>
+    <t>scarf</t>
+  </si>
+  <si>
+    <t>der Anzug</t>
+  </si>
+  <si>
+    <t>suit</t>
+  </si>
+  <si>
+    <t>die Bluse</t>
+  </si>
+  <si>
+    <t>blouse</t>
+  </si>
+  <si>
+    <t>der Stiefel</t>
+  </si>
+  <si>
+    <t>boot</t>
+  </si>
+  <si>
+    <t>die Sandale</t>
+  </si>
+  <si>
+    <t>sandal</t>
+  </si>
+  <si>
+    <t>der Knopf</t>
+  </si>
+  <si>
+    <t>button</t>
+  </si>
+  <si>
+    <t>der Reißverschluss</t>
+  </si>
+  <si>
+    <t>zipper</t>
+  </si>
+  <si>
+    <t>die Farbe</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>die Größe</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>die Gesundheit</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>der Arzt</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>die Ärztin</t>
+  </si>
+  <si>
+    <t>female doctor</t>
+  </si>
+  <si>
+    <t>das Krankenhaus</t>
+  </si>
+  <si>
+    <t>hospital</t>
+  </si>
+  <si>
+    <t>die Apotheke</t>
+  </si>
+  <si>
+    <t>pharmacy</t>
+  </si>
+  <si>
+    <t>die Medizin</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>das Rezept</t>
+  </si>
+  <si>
+    <t>prescription</t>
+  </si>
+  <si>
+    <t>der Patient</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>die Krankheit</t>
+  </si>
+  <si>
+    <t>illness</t>
+  </si>
+  <si>
+    <t>das Fieber</t>
+  </si>
+  <si>
+    <t>fever</t>
+  </si>
+  <si>
+    <t>der Kopf</t>
+  </si>
+  <si>
+    <t>head</t>
+  </si>
+  <si>
+    <t>das Auge</t>
+  </si>
+  <si>
+    <t>eye</t>
+  </si>
+  <si>
+    <t>das Ohr</t>
+  </si>
+  <si>
+    <t>ear</t>
+  </si>
+  <si>
+    <t>die Nase</t>
+  </si>
+  <si>
+    <t>nose</t>
+  </si>
+  <si>
+    <t>der Mund</t>
+  </si>
+  <si>
+    <t>mouth</t>
+  </si>
+  <si>
+    <t>der Zahn</t>
+  </si>
+  <si>
+    <t>tooth</t>
+  </si>
+  <si>
+    <t>der Hals</t>
+  </si>
+  <si>
+    <t>throat</t>
+  </si>
+  <si>
+    <t>die Hand</t>
+  </si>
+  <si>
+    <t>hand</t>
+  </si>
+  <si>
+    <t>der Arm</t>
+  </si>
+  <si>
+    <t>arm</t>
+  </si>
+  <si>
+    <t>das Bein</t>
+  </si>
+  <si>
+    <t>leg</t>
+  </si>
+  <si>
+    <t>der Fuß</t>
+  </si>
+  <si>
+    <t>foot</t>
+  </si>
+  <si>
+    <t>das Herz</t>
+  </si>
+  <si>
+    <t>heart</t>
+  </si>
+  <si>
+    <t>der Rücken</t>
+  </si>
+  <si>
+    <t>back</t>
+  </si>
+  <si>
+    <t>der Bauch</t>
+  </si>
+  <si>
+    <t>stomach</t>
+  </si>
+  <si>
+    <t>die Schmerzen</t>
+  </si>
+  <si>
+    <t>pain</t>
+  </si>
+  <si>
+    <t>der Husten</t>
+  </si>
+  <si>
+    <t>cough</t>
+  </si>
+  <si>
+    <t>die Erkältung</t>
+  </si>
+  <si>
+    <t>die Hilfe</t>
+  </si>
+  <si>
+    <t>help</t>
+  </si>
+  <si>
+    <t>der Notruf</t>
+  </si>
+  <si>
+    <t>emergency call</t>
+  </si>
+  <si>
+    <t>die Versicherung</t>
+  </si>
+  <si>
+    <t>insurance</t>
+  </si>
+  <si>
+    <t>das Einkaufen</t>
+  </si>
+  <si>
+    <t>shopping</t>
+  </si>
+  <si>
+    <t>das Geschäft</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>der Supermarkt</t>
+  </si>
+  <si>
+    <t>supermarket</t>
+  </si>
+  <si>
+    <t>der Markt</t>
+  </si>
+  <si>
+    <t>market</t>
+  </si>
+  <si>
+    <t>das Kaufhaus</t>
+  </si>
+  <si>
+    <t>department store</t>
+  </si>
+  <si>
+    <t>der Preis</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>die Kasse</t>
+  </si>
+  <si>
+    <t>checkout</t>
+  </si>
+  <si>
+    <t>receipt/bill</t>
+  </si>
+  <si>
+    <t>die Tüte</t>
+  </si>
+  <si>
+    <t>der Euro</t>
+  </si>
+  <si>
+    <t>euro</t>
+  </si>
+  <si>
+    <t>die Münze</t>
+  </si>
+  <si>
+    <t>coin</t>
+  </si>
+  <si>
+    <t>der Schein</t>
+  </si>
+  <si>
+    <t>banknote</t>
+  </si>
+  <si>
+    <t>das Angebot</t>
+  </si>
+  <si>
+    <t>offer</t>
+  </si>
+  <si>
+    <t>der Rabatt</t>
+  </si>
+  <si>
+    <t>discount</t>
+  </si>
+  <si>
+    <t>das Produkt</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>clothes</t>
+  </si>
+  <si>
+    <t>das Obst</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>das Gemüse</t>
+  </si>
+  <si>
+    <t>vegetables</t>
+  </si>
+  <si>
+    <t>der Einkaufswagen</t>
+  </si>
+  <si>
+    <t>shopping cart</t>
+  </si>
+  <si>
+    <t>die Öffnungszeit</t>
+  </si>
+  <si>
+    <t>opening hours</t>
+  </si>
+  <si>
+    <t>My Definition</t>
+  </si>
+  <si>
+    <t>ec2 are the instances to run virtual servers and manage on your own.</t>
+  </si>
+  <si>
+    <t>ecr is the container register where docker images will be stored, which will later pick by ecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecs wil pick docker images from ecr and run it on ecs2 instances. </t>
+  </si>
+  <si>
+    <t>here it will created the ec2 instance and run the application. We have to pay for ec2 instance even no body use app.</t>
+  </si>
+  <si>
+    <t>here code will be dployed and there is no ec2 server, so no need to pay if app is not in use.</t>
+  </si>
+  <si>
+    <t>it upgrade/downgrade number of ec2 instances.</t>
+  </si>
+  <si>
+    <t>it will support sq, postress, oracle, aurora.</t>
+  </si>
+  <si>
+    <t>it has high availability, scalability and performance than rds. Best for postres and my sql, sql server is not supported.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -660,6 +2778,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -681,7 +2823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -706,6 +2848,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -986,22 +3149,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="35.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1796875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1009,22 +3173,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1032,22 +3199,25 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1055,22 +3225,25 @@
         <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1078,22 +3251,25 @@
         <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="63" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1101,22 +3277,25 @@
         <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1124,22 +3303,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1147,114 +3329,121 @@
         <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="63" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -1262,22 +3451,25 @@
         <v>67</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1285,405 +3477,2589 @@
         <v>73</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" s="2" customFormat="1" ht="42" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="50.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>116</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C21" s="7"/>
       <c r="D21" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>122</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>128</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C23" s="7"/>
       <c r="D23" s="7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>134</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>135</v>
+        <v>329</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>136</v>
+        <v>330</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>137</v>
+        <v>331</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
-        <v>24</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="8" t="s">
+    </row>
+    <row r="27" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A27" s="6">
+        <v>27</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E27" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F27" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G27" s="6" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>26</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="H27" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="8" t="s">
+    </row>
+    <row r="28" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A28" s="6">
+        <v>28</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E28" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F28" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G28" s="6" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>27</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="C28" s="6" t="s">
+    </row>
+    <row r="29" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A29" s="6">
+        <v>29</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="C29" s="6"/>
+      <c r="D29" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="6" t="s">
+    </row>
+    <row r="30" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>30</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="C30" s="6"/>
+      <c r="D30" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E30" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G30" s="6" t="s">
         <v>200</v>
       </c>
+      <c r="H30" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>31</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>32</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
+        <v>33</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>217</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H33" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:T31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>819</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>808</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>792</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>797</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>801</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>806</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C21" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>833</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C22" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="T22" s="9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C23" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="T23" s="9" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C24" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C25" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C26" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="T26" s="9" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C27" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="T27" s="9" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C28" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="R28" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C29" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>811</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C30" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>830</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="T30" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C31" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="R31" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>874</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S2:T39">
+    <sortCondition descending="1" ref="S1:S39"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80A45CB5-28C5-4B36-9957-7292545F4CA4}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B21">
+    <sortCondition descending="1" ref="A1:A21"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1691,136 +6067,713 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" t="s">
         <v>147</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B6" t="s">
         <v>149</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B7" t="s">
         <v>151</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B8" t="s">
         <v>153</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B9" t="s">
         <v>155</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B10" t="s">
         <v>157</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B11" t="s">
         <v>159</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B12" t="s">
         <v>161</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B13" t="s">
         <v>163</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B14" t="s">
         <v>165</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B15" t="s">
         <v>167</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B16" t="s">
         <v>169</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B17" t="s">
         <v>171</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B2:M183"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.1796875" style="11"/>
+    <col min="2" max="2" width="45.7265625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="9.1796875" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="31" x14ac:dyDescent="0.35">
+      <c r="B2" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B6" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="I7" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C14" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B17" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="I21" s="13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B22" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C25" s="11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C26" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="I28" s="13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B29" s="13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="I30" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B31" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B32" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" ht="31" x14ac:dyDescent="0.35">
+      <c r="B33" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B34" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B35" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B37" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B38" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B39" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B40" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="I41" s="11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B42" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B44" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="I45" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="M45" s="13" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B46" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="I47" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B48" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="I49" s="11" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B16" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" t="s">
-        <v>176</v>
+      <c r="M49" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" s="11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="M51" s="11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B52" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" ht="31" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="I56" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B58" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="I59" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B60" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C61" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C62" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C63" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B64" s="13" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" s="11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" s="11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" s="11" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B71" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="B156" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B158" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="B160" s="14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B163" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B164" s="11" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B165" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B166" s="11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B167" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B168" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B169" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B170" s="11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B171" s="11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B172" s="11" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B173" s="11" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B174" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B175" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B176" s="11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B177" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B178" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B179" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B180" s="11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B181" s="11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B183" s="11" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
